--- a/results/5Fold_support.xlsx
+++ b/results/5Fold_support.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,25 +513,25 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5818248275108028</v>
+        <v>0.5815177260173958</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5808132097279911</v>
+        <v>0.5798772113802482</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6204640429425174</v>
+        <v>0.6167683451074097</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2223188322754941</v>
+        <v>0.2242943239626383</v>
       </c>
       <c r="L2" t="n">
-        <v>0.336785557440349</v>
+        <v>0.3310859135219029</v>
       </c>
     </row>
     <row r="3">
@@ -560,22 +560,22 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5806399233359099</v>
+        <v>0.5815363883564821</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5791609185527469</v>
+        <v>0.5801514875818088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6194218405542814</v>
+        <v>0.6235595861956822</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2230083803021249</v>
+        <v>0.2224444059845654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3368845709732601</v>
+        <v>0.3898888349533082</v>
       </c>
     </row>
     <row r="4">
@@ -601,25 +601,25 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>2025</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>0.580356397893463</v>
+        <v>0.581409429756239</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5793562701204541</v>
+        <v>0.5799895633180463</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6185354459898059</v>
+        <v>0.6237149694668752</v>
       </c>
       <c r="K4" t="n">
-        <v>0.22236551619773</v>
+        <v>0.2229164717428072</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3369539448193141</v>
+        <v>0.3994796361242022</v>
       </c>
     </row>
     <row r="5">
@@ -645,25 +645,25 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>114514</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5786463405890849</v>
+        <v>0.5813230396475511</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5777189559031033</v>
+        <v>0.5799371998272448</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6158428665980591</v>
+        <v>0.6236187912540199</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2225904691622319</v>
+        <v>0.2229780034518837</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3369714719908578</v>
+        <v>0.4001417125974383</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ordsurv</t>
+          <t>deepsurv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -689,25 +689,25 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5802008005626291</v>
+        <v>0.5852343138206914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5789487603411192</v>
+        <v>0.5860950577957335</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6184472022569144</v>
+        <v>0.6098615190749697</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2224353970306835</v>
+        <v>0.5603254129531129</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3368659538882119</v>
+        <v>4.956173256465367</v>
       </c>
     </row>
     <row r="7">
@@ -733,25 +733,25 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5859625842045626</v>
+        <v>0.5852343138206914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5867558706798414</v>
+        <v>0.5860950577957335</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6129081796934315</v>
+        <v>0.6155398256265546</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5167029202170201</v>
+        <v>0.4225495842991823</v>
       </c>
       <c r="L7" t="n">
-        <v>4.950625705718994</v>
+        <v>4.956173256465367</v>
       </c>
     </row>
     <row r="8">
@@ -780,7 +780,7 @@
         <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
         <v>0.5852343138206914</v>
@@ -789,10 +789,10 @@
         <v>0.5860950577957335</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6125981179801532</v>
+        <v>0.6207503887418062</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5030748164601995</v>
+        <v>0.3113561985613609</v>
       </c>
       <c r="L8" t="n">
         <v>4.956173256465367</v>
@@ -821,25 +821,25 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>2025</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5849348992945921</v>
+        <v>0.5852343138206914</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5867259356311216</v>
+        <v>0.5860950577957335</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6109238788080794</v>
+        <v>0.6207504342730511</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4770819452708565</v>
+        <v>0.2794591776858932</v>
       </c>
       <c r="L9" t="n">
-        <v>4.953219100407192</v>
+        <v>4.956173256465367</v>
       </c>
     </row>
     <row r="10">
@@ -850,7 +850,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>deepsurv</t>
+          <t>deephit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -865,25 +865,25 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>114514</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5827979973967431</v>
+        <v>0.5774874309975859</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5836346158350709</v>
+        <v>0.5786139139237144</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6088361067936383</v>
+        <v>0.6171179451138828</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4871589886864511</v>
+        <v>0.2139097235839412</v>
       </c>
       <c r="L10" t="n">
-        <v>4.953144236973353</v>
+        <v>1.197472654070173</v>
       </c>
     </row>
     <row r="11">
@@ -894,7 +894,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>deepsurv</t>
+          <t>deephit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -909,25 +909,25 @@
         <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5832734782967691</v>
+        <v>0.5763956925362723</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5845777540684196</v>
+        <v>0.5776618338897397</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6096884641577465</v>
+        <v>0.6247692961239009</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4772500961414144</v>
+        <v>0.2113793596366771</v>
       </c>
       <c r="L11" t="n">
-        <v>4.953138855525426</v>
+        <v>1.938978675433568</v>
       </c>
     </row>
     <row r="12">
@@ -953,421 +953,25 @@
         <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5166137221073857</v>
+        <v>0.5750302540433128</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5155033768371042</v>
+        <v>0.5762076637459705</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6207169857098309</v>
+        <v>0.621760143335745</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2110434539820347</v>
+        <v>0.2118361728043996</v>
       </c>
       <c r="L12" t="n">
-        <v>1.500400114059448</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>deephit</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F13" t="n">
-        <v>42</v>
-      </c>
-      <c r="G13" t="n">
-        <v>25</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5158354704717855</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.5148503122899342</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.6219576327220973</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.2117944259452377</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.50123085294451</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>deephit</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>100</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G14" t="n">
-        <v>25</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5150728183138983</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.5141547588510557</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.619022255282538</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2114197155799596</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.501227171080453</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>deephit</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>100</v>
-      </c>
-      <c r="F15" t="n">
-        <v>114514</v>
-      </c>
-      <c r="G15" t="n">
-        <v>25</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.515815512735734</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.5146715257913252</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6204756367591548</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.2115618905531023</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.500800572122846</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>deephit</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>100</v>
-      </c>
-      <c r="F16" t="n">
-        <v>777</v>
-      </c>
-      <c r="G16" t="n">
-        <v>25</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5162699407181213</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.5152044340468672</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.6211514156807413</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.211162350993656</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.501092239788601</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>discrete</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>100</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>25</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.5802864700313248</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.5789071289565351</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.6239185941193776</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.2195418594067335</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2.431025634493147</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>discrete</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>100</v>
-      </c>
-      <c r="F18" t="n">
-        <v>42</v>
-      </c>
-      <c r="G18" t="n">
-        <v>25</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5806586826236617</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.5792462297469883</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.6249195083262713</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.2201910529384215</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2.432470233099802</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>discrete</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>100</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G19" t="n">
-        <v>25</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5792432012110191</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.5779370755388042</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.6225848083651951</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.2197664469405751</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.43164734840393</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>discrete</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" t="n">
-        <v>114514</v>
-      </c>
-      <c r="G20" t="n">
-        <v>25</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.5796557090683673</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.5781039647936933</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.6236702290318552</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.2199656428810279</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2.431639562334333</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>support</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>discrete</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" t="n">
-        <v>777</v>
-      </c>
-      <c r="G21" t="n">
-        <v>25</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.5801272816047549</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.5787768088045542</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.624124528602706</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.2195556228862435</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.43187678200858</v>
+        <v>2.436679560797555</v>
       </c>
     </row>
   </sheetData>
